--- a/deliverables/02-equipment/CFU-000-ME-DS-000_Equipment-Datasheets-Combined.xlsx
+++ b/deliverables/02-equipment/CFU-000-ME-DS-000_Equipment-Datasheets-Combined.xlsx
@@ -1369,7 +1369,7 @@
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>5.74 / 9.54 barg</t>
+          <t>5.74 / 9.63 barg</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="I19" s="10" t="inlineStr">
         <is>
-          <t>6.91 / 10.58 barg</t>
+          <t>6.91 / 10.62 barg</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>6900 / 4140 mm</t>
+          <t>6900 / 3500 mm</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="I33" s="10" t="inlineStr">
         <is>
-          <t>6600 / 3000 / 2600 mm</t>
+          <t>6600 / 3000 / 4400 mm</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>36.00 m</t>
+          <t>37.00 m</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>Stripping section 18, Swage 30 deg 18, Flash zone / rectifying section 16 mm</t>
+          <t>Stripping section 22, Swage 30 deg 20, Flash zone / rectifying section 16 mm</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="I35" s="10" t="inlineStr">
         <is>
-          <t>Boot (stripping / quench) 25, Lower cone 30 deg 25, Main shell (beds 2-4, flash zone) 25, Upper cone 30 deg 25, Top section (bed 1) 18 mm</t>
+          <t>Boot (stripping / quench) 28, Lower cone 30 deg 25, Main shell (beds 2-4, flash zone) 25, Upper cone 30 deg 22, Top section (bed 1) 22 mm</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="I36" s="10" t="inlineStr">
         <is>
-          <t>18 / 18 mm</t>
+          <t>22 / 18 mm</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>6.5 m / 18 mm / 4176 mm</t>
+          <t>6.5 m / 20 mm / 3544 mm</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I37" s="10" t="inlineStr">
         <is>
-          <t>6.0 m / 18 mm / 3050 mm</t>
+          <t>6.0 m / 20 mm / 3056 mm</t>
         </is>
       </c>
     </row>
@@ -2173,7 +2173,7 @@
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>EL 144.225</t>
+          <t>EL 145.225</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="I39" s="10" t="inlineStr">
         <is>
-          <t>EL 142.650</t>
+          <t>EL 143.100</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>32 x M48 F1554 Gr.55 on 4426 BCD</t>
+          <t>28 x M64 F1554 Gr.55 on 3794 BCD</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="I40" s="10" t="inlineStr">
         <is>
-          <t>24 x M64 F1554 Gr.55 on 3300 BCD</t>
+          <t>24 x M64 F1554 Gr.55 on 3306 BCD</t>
         </is>
       </c>
     </row>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="I41" s="10" t="inlineStr">
         <is>
-          <t>Boot (stripping / quench): 2 x 160x16 FB @ 3.0 m; Main shell (beds 2-4, flash zone): 5 x 300x25 FB @ 3.0 m; Top section (bed 1): 1 x 140x16 FB @ 3.0 m</t>
+          <t>Boot (stripping / quench): 3 x 160x16 FB @ 3.0 m; Main shell (beds 2-4, flash zone): 5 x 300x25 FB @ 3.0 m; Top section (bed 1): 1 x 220x20 FB @ 3.0 m</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>1.00 Hz / 1.07</t>
+          <t>0.77 Hz / 1.16</t>
         </is>
       </c>
       <c r="D44" s="10" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="I44" s="10" t="inlineStr">
         <is>
-          <t>0.81 Hz / 1.22</t>
+          <t>0.74 Hz / 1.22</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>261.7 t</t>
+          <t>258.4 t</t>
         </is>
       </c>
       <c r="D53" s="10" t="inlineStr">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="I53" s="10" t="inlineStr">
         <is>
-          <t>244.0 t</t>
+          <t>267.2 t</t>
         </is>
       </c>
     </row>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>337.4 t</t>
+          <t>329.6 t</t>
         </is>
       </c>
       <c r="D54" s="10" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="I54" s="10" t="inlineStr">
         <is>
-          <t>294.0 t</t>
+          <t>320.5 t</t>
         </is>
       </c>
     </row>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t>423.0 t</t>
+          <t>405.0 t</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="I55" s="10" t="inlineStr">
         <is>
-          <t>337.1 t</t>
+          <t>366.9 t</t>
         </is>
       </c>
     </row>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>1554.5 t</t>
+          <t>1458.2 t</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="I56" s="10" t="inlineStr">
         <is>
-          <t>1043.4 t</t>
+          <t>1128.0 t</t>
         </is>
       </c>
     </row>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t>756 kN</t>
+          <t>801 kN</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="I57" s="10" t="inlineStr">
         <is>
-          <t>650 kN</t>
+          <t>692 kN</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t>19490 kNm</t>
+          <t>21781 kNm</t>
         </is>
       </c>
       <c r="D58" s="10" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="I58" s="10" t="inlineStr">
         <is>
-          <t>15673 kNm</t>
+          <t>17661 kNm</t>
         </is>
       </c>
     </row>
@@ -2978,7 +2978,7 @@
       <c r="H60" s="10" t="inlineStr"/>
       <c r="I60" s="10" t="inlineStr">
         <is>
-          <t>2.50 m, ID 2600</t>
+          <t>2.50 m, ID 4400</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>EL 116.710</t>
+          <t>EL 118.760</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>EL 140.850</t>
+          <t>EL 142.150</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>EL 140.800</t>
+          <t>EL 142.100</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>EL 138.830</t>
+          <t>EL 140.130</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>EL 134.250</t>
+          <t>EL 135.550</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>EL 132.280</t>
+          <t>EL 133.580</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>EL 126.480</t>
+          <t>EL 127.780</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>EL 124.510</t>
+          <t>EL 125.810</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>EL 134.410</t>
+          <t>EL 135.710</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>EL 134.920</t>
+          <t>EL 136.220</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>EL 126.640</t>
+          <t>EL 127.940</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>EL 127.150</t>
+          <t>EL 128.450</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>EL 120.090</t>
+          <t>EL 121.390</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>EL 120.600</t>
+          <t>EL 121.900</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>EL 107.770</t>
+          <t>EL 111.216</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>EL 106.800</t>
+          <t>EL 106.700</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>EL 118.260</t>
+          <t>EL 119.560</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4099,7 +4099,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>EL 141.500</t>
+          <t>EL 142.800</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>EL 135.475</t>
+          <t>EL 136.775</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>EL 129.535</t>
+          <t>EL 130.835</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>EL 122.375</t>
+          <t>EL 123.675</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4267,7 +4267,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>EL 115.310</t>
+          <t>EL 118.610</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>EL 109.895</t>
+          <t>EL 113.341</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>EL 107.020</t>
+          <t>EL 110.566</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>16"</t>
+          <t>18"</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -7274,7 +7274,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>EL 118.886</t>
+          <t>EL 120.145</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -7400,7 +7400,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>EL 136.350</t>
+          <t>EL 137.250</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>EL 132.886</t>
+          <t>EL 134.445</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -7484,7 +7484,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>EL 128.086</t>
+          <t>EL 129.645</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>EL 128.086</t>
+          <t>EL 129.345</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>300 deg</t>
+          <t>100 deg</t>
         </is>
       </c>
     </row>
@@ -7568,7 +7568,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>EL 123.186</t>
+          <t>EL 124.445</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>EL 120.336</t>
+          <t>EL 121.595</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -7652,7 +7652,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>EL 110.738</t>
+          <t>EL 112.297</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>EL 137.550</t>
+          <t>EL 136.950</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -7946,7 +7946,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>EL 129.286</t>
+          <t>EL 130.845</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -7988,7 +7988,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>EL 123.486</t>
+          <t>EL 124.745</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -8030,7 +8030,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>EL 117.686</t>
+          <t>EL 119.245</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>0.110</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -11421,7 +11421,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>14.69 / 16.70 MW</t>
+          <t>14.69 / 17.49 MW</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>88 % (see note 3)</t>
+          <t>84 % (see note 3)</t>
         </is>
       </c>
     </row>
@@ -11665,7 +11665,7 @@
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>1279 kg/h</t>
+          <t>1340 kg/h</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>24 t/h</t>
+          <t>25 t/h</t>
         </is>
       </c>
     </row>
@@ -11714,12 +11714,12 @@
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>1044 C</t>
+          <t>954 C</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>854 C</t>
+          <t>822 C</t>
         </is>
       </c>
     </row>
@@ -11922,12 +11922,12 @@
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>128  |  64 (2 shock rows)</t>
+          <t>144  |  64 (2 shock rows)</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>40  |  20 (2 shock rows)</t>
+          <t>44  |  20 (2 shock rows)</t>
         </is>
       </c>
     </row>
@@ -11976,12 +11976,12 @@
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>Single row on side walls, 32 per wall per cell  |  8 per row, staggered</t>
+          <t>Single row on side walls, 36 per wall per cell  |  8 per row, staggered</t>
         </is>
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>Single row on side walls, 20 per wall per cell  |  4 per row, staggered</t>
+          <t>Single row on side walls, 22 per wall per cell  |  4 per row, staggered</t>
         </is>
       </c>
     </row>
@@ -12012,12 +12012,12 @@
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>1229 m2  |  607 m2 bare-equiv.</t>
+          <t>1323 m2  |  563 m2 bare-equiv.</t>
         </is>
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>382 m2  |  185 m2 bare-equiv.</t>
+          <t>411 m2  |  188 m2 bare-equiv.</t>
         </is>
       </c>
     </row>
@@ -12161,7 +12161,7 @@
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>Utility coil 2 rows (1.4 MW, TBD)</t>
+          <t>Utility coil 2 rows (0.8 MW, TBD)</t>
         </is>
       </c>
     </row>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>2.78 / 3.48 MW</t>
+          <t>2.92 / 3.64 MW</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>21.9 x 12.7 m (plot reservation 26.0 x 12.7 m)</t>
+          <t>21.9 x 12.7 m (plot reservation 21.9 x 25.4 m)</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t>21.9 x 5.4 m (plot reservation 14.0 x 11.0 m)</t>
+          <t>21.9 x 5.4 m (plot reservation 21.9 x 11.1 m)</t>
         </is>
       </c>
     </row>
@@ -12356,12 +12356,12 @@
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>18.9 x 5.85 x 13.0 m</t>
+          <t>18.9 x 5.85 x 14.3 m</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>18.9 x 4.90 x 8.9 m</t>
+          <t>18.9 x 4.90 x 9.6 m</t>
         </is>
       </c>
     </row>
@@ -12415,7 +12415,7 @@
       </c>
       <c r="D67" s="10" t="inlineStr">
         <is>
-          <t>1.2 m / EL 132.000</t>
+          <t>1.3 m / EL 132.000</t>
         </is>
       </c>
     </row>
@@ -12554,12 +12554,12 @@
       </c>
       <c r="C75" s="10" t="inlineStr">
         <is>
-          <t>1033 / 1059 t (+/-30 %)</t>
+          <t>1077 / 1106 t (+/-30 %)</t>
         </is>
       </c>
       <c r="D75" s="10" t="inlineStr">
         <is>
-          <t>328 / 337 t (+/-30 %)</t>
+          <t>340 / 349 t (+/-30 %)</t>
         </is>
       </c>
     </row>
@@ -12846,12 +12846,12 @@
       </c>
       <c r="O4" s="10" t="inlineStr">
         <is>
-          <t>1950-6096 AKT  (ID mm - tube length mm)</t>
+          <t>900-6096 AKT  (ID mm - tube length mm)</t>
         </is>
       </c>
       <c r="P4" s="10" t="inlineStr">
         <is>
-          <t>750-6096 AES  (ID mm - tube length mm)</t>
+          <t>650-6096 AES  (ID mm - tube length mm)</t>
         </is>
       </c>
       <c r="Q4" s="10" t="inlineStr">
@@ -12861,7 +12861,7 @@
       </c>
       <c r="R4" s="10" t="inlineStr">
         <is>
-          <t>1200-6096 BKT  (ID mm - tube length mm)</t>
+          <t>1300-6096 BKT  (ID mm - tube length mm)</t>
         </is>
       </c>
       <c r="S4" s="10" t="inlineStr">
@@ -13072,12 +13072,12 @@
       </c>
       <c r="O6" s="10" t="inlineStr">
         <is>
-          <t>648 / 648 m2</t>
+          <t>84 / 84 m2</t>
         </is>
       </c>
       <c r="P6" s="10" t="inlineStr">
         <is>
-          <t>117 / 117 m2</t>
+          <t>86 / 86 m2</t>
         </is>
       </c>
       <c r="Q6" s="10" t="inlineStr">
@@ -13087,7 +13087,7 @@
       </c>
       <c r="R6" s="10" t="inlineStr">
         <is>
-          <t>190 / 190 m2</t>
+          <t>242 / 242 m2</t>
         </is>
       </c>
       <c r="S6" s="10" t="inlineStr">
@@ -13411,7 +13411,7 @@
       </c>
       <c r="O9" s="10" t="inlineStr">
         <is>
-          <t>7.62 MW</t>
+          <t>1.78 MW</t>
         </is>
       </c>
       <c r="P9" s="10" t="inlineStr">
@@ -13426,7 +13426,7 @@
       </c>
       <c r="R9" s="10" t="inlineStr">
         <is>
-          <t>8.51 MW</t>
+          <t>10.83 MW</t>
         </is>
       </c>
       <c r="S9" s="10" t="inlineStr">
@@ -13524,12 +13524,12 @@
       </c>
       <c r="O10" s="10" t="inlineStr">
         <is>
-          <t>78.3 C (approx.)</t>
+          <t>118.3 C (approx.)</t>
         </is>
       </c>
       <c r="P10" s="10" t="inlineStr">
         <is>
-          <t>84.2 C (approx.)</t>
+          <t>114.7 C (approx.)</t>
         </is>
       </c>
       <c r="Q10" s="10" t="inlineStr">
@@ -13892,7 +13892,7 @@
       </c>
       <c r="O14" s="10" t="inlineStr">
         <is>
-          <t>12.9 / 108.3 t/h</t>
+          <t>3.0 / 108.3 t/h</t>
         </is>
       </c>
       <c r="P14" s="10" t="inlineStr">
@@ -13907,7 +13907,7 @@
       </c>
       <c r="R14" s="10" t="inlineStr">
         <is>
-          <t>102.1 / 18.0 t/h</t>
+          <t>129.9 / 22.9 t/h</t>
         </is>
       </c>
       <c r="S14" s="10" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="P15" s="10" t="inlineStr">
         <is>
-          <t>77 / 203 C</t>
+          <t>45 / 203 C</t>
         </is>
       </c>
       <c r="Q15" s="10" t="inlineStr">
@@ -14118,12 +14118,12 @@
       </c>
       <c r="O16" s="10" t="inlineStr">
         <is>
-          <t>148 / 175 C</t>
+          <t>148 / 255 C</t>
         </is>
       </c>
       <c r="P16" s="10" t="inlineStr">
         <is>
-          <t>120 / 163 C</t>
+          <t>91 / 163 C</t>
         </is>
       </c>
       <c r="Q16" s="10" t="inlineStr">
@@ -14840,12 +14840,12 @@
       </c>
       <c r="R23" s="10" t="inlineStr">
         <is>
-          <t>285 C</t>
+          <t>430 C</t>
         </is>
       </c>
       <c r="S23" s="10" t="inlineStr">
         <is>
-          <t>215 C</t>
+          <t>280 C</t>
         </is>
       </c>
       <c r="T23" s="10" t="inlineStr">
@@ -15410,7 +15410,7 @@
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>3" 150#</t>
+          <t>3" 300#</t>
         </is>
       </c>
       <c r="T28" s="10" t="inlineStr">
@@ -15503,12 +15503,12 @@
       </c>
       <c r="O29" s="10" t="inlineStr">
         <is>
-          <t>1820 / 19.05 mm / 14 BWG (2.11 mm) / 6096 mm</t>
+          <t>236 / 19.05 mm / 14 BWG (2.11 mm) / 6096 mm</t>
         </is>
       </c>
       <c r="P29" s="10" t="inlineStr">
         <is>
-          <t>248 / 25.4 mm / 12 BWG (2.77 mm) / 6096 mm</t>
+          <t>182 / 25.4 mm / 12 BWG (2.77 mm) / 6096 mm</t>
         </is>
       </c>
       <c r="Q29" s="10" t="inlineStr">
@@ -15518,7 +15518,7 @@
       </c>
       <c r="R29" s="10" t="inlineStr">
         <is>
-          <t>535 / 19.05 mm / 14 BWG (2.11 mm) / 6096 mm</t>
+          <t>680 / 19.05 mm / 14 BWG (2.11 mm) / 6096 mm</t>
         </is>
       </c>
       <c r="S29" s="10" t="inlineStr">
@@ -15842,12 +15842,12 @@
       </c>
       <c r="O32" s="10" t="inlineStr">
         <is>
-          <t>SA-516-70 / 1950 mm / 16 mm</t>
+          <t>SA-516-70 / 900 mm / 12 mm</t>
         </is>
       </c>
       <c r="P32" s="10" t="inlineStr">
         <is>
-          <t>SA-516-70 / 750 mm / 10 mm</t>
+          <t>SA-516-70 / 650 mm / 10 mm</t>
         </is>
       </c>
       <c r="Q32" s="10" t="inlineStr">
@@ -15857,7 +15857,7 @@
       </c>
       <c r="R32" s="10" t="inlineStr">
         <is>
-          <t>SA-516-70 / 1200 mm / 14 mm</t>
+          <t>SA-516-70 / 1300 mm / 18 mm</t>
         </is>
       </c>
       <c r="S32" s="10" t="inlineStr">
@@ -15955,7 +15955,7 @@
       </c>
       <c r="O33" s="10" t="inlineStr">
         <is>
-          <t>14 mm</t>
+          <t>10 mm</t>
         </is>
       </c>
       <c r="P33" s="10" t="inlineStr">
@@ -15970,7 +15970,7 @@
       </c>
       <c r="R33" s="10" t="inlineStr">
         <is>
-          <t>20 mm</t>
+          <t>32 mm</t>
         </is>
       </c>
       <c r="S33" s="10" t="inlineStr">
@@ -16972,12 +16972,12 @@
       </c>
       <c r="O42" s="10" t="inlineStr">
         <is>
-          <t>24.2 / 46.4 t</t>
+          <t>4.9 / 9.6 t</t>
         </is>
       </c>
       <c r="P42" s="10" t="inlineStr">
         <is>
-          <t>6.4 / 9.7 t</t>
+          <t>5.0 / 7.4 t</t>
         </is>
       </c>
       <c r="Q42" s="10" t="inlineStr">
@@ -16987,7 +16987,7 @@
       </c>
       <c r="R42" s="10" t="inlineStr">
         <is>
-          <t>9.5 / 18.0 t</t>
+          <t>12.9 / 22.8 t</t>
         </is>
       </c>
       <c r="S42" s="10" t="inlineStr">
@@ -17085,12 +17085,12 @@
       </c>
       <c r="O43" s="10" t="inlineStr">
         <is>
-          <t>23.2 t</t>
+          <t>3.0 t</t>
         </is>
       </c>
       <c r="P43" s="10" t="inlineStr">
         <is>
-          <t>3.2 t</t>
+          <t>2.3 t</t>
         </is>
       </c>
       <c r="Q43" s="10" t="inlineStr">
@@ -17100,7 +17100,7 @@
       </c>
       <c r="R43" s="10" t="inlineStr">
         <is>
-          <t>6.8 t</t>
+          <t>8.7 t</t>
         </is>
       </c>
       <c r="S43" s="10" t="inlineStr">
@@ -17319,7 +17319,7 @@
       </c>
       <c r="E5" s="10" t="inlineStr">
         <is>
-          <t>8.16 MW</t>
+          <t>3.72 MW</t>
         </is>
       </c>
       <c r="F5" s="10" t="inlineStr">
@@ -17531,7 +17531,7 @@
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>205 / 55 C</t>
+          <t>128 / 55 C</t>
         </is>
       </c>
       <c r="F9" s="10" t="inlineStr">
@@ -17720,7 +17720,7 @@
       </c>
       <c r="K12" s="10" t="inlineStr">
         <is>
-          <t>35 / 85 C</t>
+          <t>35 / 60 C</t>
         </is>
       </c>
     </row>
@@ -17743,7 +17743,7 @@
       </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
-          <t>541 kg/s</t>
+          <t>247 kg/s</t>
         </is>
       </c>
       <c r="F13" s="10" t="inlineStr">
@@ -17773,7 +17773,7 @@
       </c>
       <c r="K13" s="10" t="inlineStr">
         <is>
-          <t>132 kg/s</t>
+          <t>264 kg/s</t>
         </is>
       </c>
     </row>
@@ -17866,7 +17866,7 @@
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>Induced draft, pipe-rack mounted</t>
+          <t>Forced draft, pipe-rack mounted</t>
         </is>
       </c>
       <c r="F16" s="10" t="inlineStr">
@@ -17909,7 +17909,7 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>2 / 4</t>
+          <t>3 / 4</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>1 / 2</t>
+          <t>2 / 2</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr">
@@ -18068,7 +18068,7 @@
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
@@ -18078,22 +18078,22 @@
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="F20" s="10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G20" s="10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H20" s="10" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr">
@@ -18131,7 +18131,7 @@
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>430 m2</t>
+          <t>302 m2</t>
         </is>
       </c>
       <c r="F21" s="10" t="inlineStr">
@@ -18161,7 +18161,7 @@
       </c>
       <c r="K21" s="10" t="inlineStr">
         <is>
-          <t>403 m2</t>
+          <t>361 m2</t>
         </is>
       </c>
     </row>
@@ -18184,7 +18184,7 @@
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>9,025 m2</t>
+          <t>6,352 m2</t>
         </is>
       </c>
       <c r="F22" s="10" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="K22" s="10" t="inlineStr">
         <is>
-          <t>8,453 m2</t>
+          <t>7,586 m2</t>
         </is>
       </c>
     </row>
@@ -18343,7 +18343,7 @@
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>Al 1100, embedded (G-fin) 57.2 mm OD, 433 fins/m</t>
+          <t>Al 1100, L-footed / extruded, 57.2 mm OD</t>
         </is>
       </c>
       <c r="F25" s="10" t="inlineStr">
@@ -18449,7 +18449,7 @@
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>9.7 barg / 235 C</t>
+          <t>9.7 barg / 160 C</t>
         </is>
       </c>
       <c r="F27" s="10" t="inlineStr">
@@ -18721,32 +18721,32 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
+          <t>2 / 6</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>2 / 2</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>2 / 2</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>2 / 2</t>
+        </is>
+      </c>
+      <c r="G33" s="10" t="inlineStr">
+        <is>
+          <t>2 / 2</t>
+        </is>
+      </c>
+      <c r="H33" s="10" t="inlineStr">
+        <is>
           <t>2 / 4</t>
-        </is>
-      </c>
-      <c r="D33" s="10" t="inlineStr">
-        <is>
-          <t>2 / 2</t>
-        </is>
-      </c>
-      <c r="E33" s="10" t="inlineStr">
-        <is>
-          <t>2 / 2</t>
-        </is>
-      </c>
-      <c r="F33" s="10" t="inlineStr">
-        <is>
-          <t>2 / 2</t>
-        </is>
-      </c>
-      <c r="G33" s="10" t="inlineStr">
-        <is>
-          <t>2 / 2</t>
-        </is>
-      </c>
-      <c r="H33" s="10" t="inlineStr">
-        <is>
-          <t>2 / 2</t>
         </is>
       </c>
       <c r="I33" s="10" t="inlineStr">
@@ -18880,7 +18880,7 @@
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>90 / 67.5 kW</t>
+          <t>55 / 45.0 kW</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr">
@@ -18890,7 +18890,7 @@
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
-          <t>45 / 32.6 kW</t>
+          <t>18.5 / 14.9 kW</t>
         </is>
       </c>
       <c r="F36" s="10" t="inlineStr">
@@ -18905,7 +18905,7 @@
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>45 / 38.5 kW</t>
+          <t>30 / 19.3 kW</t>
         </is>
       </c>
       <c r="I36" s="10" t="inlineStr">
@@ -19251,7 +19251,7 @@
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>102.7 / 107.9 t</t>
+          <t>118.7 / 123.9 t</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
@@ -19261,7 +19261,7 @@
       </c>
       <c r="E43" s="10" t="inlineStr">
         <is>
-          <t>34.2 / 35.6 t</t>
+          <t>28.8 / 29.8 t</t>
         </is>
       </c>
       <c r="F43" s="10" t="inlineStr">
@@ -19276,7 +19276,7 @@
       </c>
       <c r="H43" s="10" t="inlineStr">
         <is>
-          <t>53.4 / 56.1 t</t>
+          <t>69.4 / 72.1 t</t>
         </is>
       </c>
       <c r="I43" s="10" t="inlineStr">
@@ -19291,7 +19291,7 @@
       </c>
       <c r="K43" s="10" t="inlineStr">
         <is>
-          <t>33.1 / 34.3 t</t>
+          <t>31.3 / 32.5 t</t>
         </is>
       </c>
     </row>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="Y5" s="10" t="inlineStr">
         <is>
-          <t>OH2</t>
+          <t>API 674/675 PD</t>
         </is>
       </c>
     </row>
@@ -21066,17 +21066,17 @@
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>3.48 barg</t>
+          <t>3.56 barg</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr">
         <is>
-          <t>3.07 barg</t>
+          <t>3.14 barg</t>
         </is>
       </c>
       <c r="J17" s="10" t="inlineStr">
         <is>
-          <t>2.68 barg</t>
+          <t>2.75 barg</t>
         </is>
       </c>
       <c r="K17" s="10" t="inlineStr">
@@ -21096,7 +21096,7 @@
       </c>
       <c r="N17" s="10" t="inlineStr">
         <is>
-          <t>1.87 barg</t>
+          <t>1.86 barg</t>
         </is>
       </c>
       <c r="O17" s="10" t="inlineStr">
@@ -21126,17 +21126,17 @@
       </c>
       <c r="T17" s="10" t="inlineStr">
         <is>
-          <t>1.53 barg</t>
+          <t>1.60 barg</t>
         </is>
       </c>
       <c r="U17" s="10" t="inlineStr">
         <is>
-          <t>0.88 barg</t>
+          <t>0.98 barg</t>
         </is>
       </c>
       <c r="V17" s="10" t="inlineStr">
         <is>
-          <t>0.36 barg</t>
+          <t>0.45 barg</t>
         </is>
       </c>
       <c r="W17" s="10" t="inlineStr">
@@ -21189,17 +21189,17 @@
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>11.48 barg</t>
+          <t>11.56 barg</t>
         </is>
       </c>
       <c r="I18" s="10" t="inlineStr">
         <is>
-          <t>11.07 barg</t>
+          <t>11.14 barg</t>
         </is>
       </c>
       <c r="J18" s="10" t="inlineStr">
         <is>
-          <t>10.68 barg</t>
+          <t>10.75 barg</t>
         </is>
       </c>
       <c r="K18" s="10" t="inlineStr">
@@ -21219,7 +21219,7 @@
       </c>
       <c r="N18" s="10" t="inlineStr">
         <is>
-          <t>13.87 barg</t>
+          <t>18.86 barg</t>
         </is>
       </c>
       <c r="O18" s="10" t="inlineStr">
@@ -21249,17 +21249,17 @@
       </c>
       <c r="T18" s="10" t="inlineStr">
         <is>
-          <t>11.53 barg</t>
+          <t>11.60 barg</t>
         </is>
       </c>
       <c r="U18" s="10" t="inlineStr">
         <is>
-          <t>10.88 barg</t>
+          <t>10.98 barg</t>
         </is>
       </c>
       <c r="V18" s="10" t="inlineStr">
         <is>
-          <t>8.36 barg</t>
+          <t>8.45 barg</t>
         </is>
       </c>
       <c r="W18" s="10" t="inlineStr">
@@ -21342,7 +21342,7 @@
       </c>
       <c r="N19" s="10" t="inlineStr">
         <is>
-          <t>12.0 bar / 172 m</t>
+          <t>17.0 bar / 244 m</t>
         </is>
       </c>
       <c r="O19" s="10" t="inlineStr">
@@ -21435,17 +21435,17 @@
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>37.2 m</t>
+          <t>38.5 m</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr">
         <is>
-          <t>30.7 m</t>
+          <t>32.0 m</t>
         </is>
       </c>
       <c r="J20" s="10" t="inlineStr">
         <is>
-          <t>22.9 m</t>
+          <t>24.2 m</t>
         </is>
       </c>
       <c r="K20" s="10" t="inlineStr">
@@ -21465,7 +21465,7 @@
       </c>
       <c r="N20" s="10" t="inlineStr">
         <is>
-          <t>5.7 m</t>
+          <t>5.6 m</t>
         </is>
       </c>
       <c r="O20" s="10" t="inlineStr">
@@ -21495,17 +21495,17 @@
       </c>
       <c r="T20" s="10" t="inlineStr">
         <is>
-          <t>34.8 m</t>
+          <t>35.7 m</t>
         </is>
       </c>
       <c r="U20" s="10" t="inlineStr">
         <is>
-          <t>26.5 m</t>
+          <t>28.1 m</t>
         </is>
       </c>
       <c r="V20" s="10" t="inlineStr">
         <is>
-          <t>18.8 m</t>
+          <t>20.0 m</t>
         </is>
       </c>
       <c r="W20" s="10" t="inlineStr">
@@ -21681,17 +21681,17 @@
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>28.5 m</t>
+          <t>29.8 m</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
         <is>
-          <t>26.5 m</t>
+          <t>27.8 m</t>
         </is>
       </c>
       <c r="J22" s="10" t="inlineStr">
         <is>
-          <t>19.3 m</t>
+          <t>20.6 m</t>
         </is>
       </c>
       <c r="K22" s="10" t="inlineStr">
@@ -21711,7 +21711,7 @@
       </c>
       <c r="N22" s="10" t="inlineStr">
         <is>
-          <t>1.5 m</t>
+          <t>1.4 m</t>
         </is>
       </c>
       <c r="O22" s="10" t="inlineStr">
@@ -21741,17 +21741,17 @@
       </c>
       <c r="T22" s="10" t="inlineStr">
         <is>
-          <t>32.1 m</t>
+          <t>33.0 m</t>
         </is>
       </c>
       <c r="U22" s="10" t="inlineStr">
         <is>
-          <t>22.3 m</t>
+          <t>23.9 m</t>
         </is>
       </c>
       <c r="V22" s="10" t="inlineStr">
         <is>
-          <t>17.7 m</t>
+          <t>19.0 m</t>
         </is>
       </c>
       <c r="W22" s="10" t="inlineStr">
@@ -21834,7 +21834,7 @@
       </c>
       <c r="N23" s="10" t="inlineStr">
         <is>
-          <t>132.6 kW</t>
+          <t>187.8 kW</t>
         </is>
       </c>
       <c r="O23" s="10" t="inlineStr">
@@ -22480,7 +22480,7 @@
       </c>
       <c r="N29" s="10" t="inlineStr">
         <is>
-          <t>188.9 kW</t>
+          <t>267.5 kW</t>
         </is>
       </c>
       <c r="O29" s="10" t="inlineStr">
@@ -22603,7 +22603,7 @@
       </c>
       <c r="N30" s="10" t="inlineStr">
         <is>
-          <t>250 kW</t>
+          <t>315 kW</t>
         </is>
       </c>
       <c r="O30" s="10" t="inlineStr">
@@ -23833,7 +23833,7 @@
       </c>
       <c r="N40" s="10" t="inlineStr">
         <is>
-          <t>5.0 t each</t>
+          <t>6.2 t each</t>
         </is>
       </c>
       <c r="O40" s="10" t="inlineStr">
@@ -24763,7 +24763,7 @@
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t>102,070 kg/h</t>
+          <t>129,912 kg/h</t>
         </is>
       </c>
       <c r="H15" s="10" t="inlineStr">
@@ -25307,7 +25307,7 @@
       </c>
       <c r="G23" s="10" t="inlineStr">
         <is>
-          <t>7,175 mm2</t>
+          <t>9,132 mm2</t>
         </is>
       </c>
       <c r="H23" s="10" t="inlineStr">
@@ -25443,7 +25443,7 @@
       </c>
       <c r="G25" s="10" t="inlineStr">
         <is>
-          <t>70 %</t>
+          <t>88 %</t>
         </is>
       </c>
       <c r="H25" s="10" t="inlineStr">

--- a/deliverables/02-equipment/CFU-000-ME-DS-000_Equipment-Datasheets-Combined.xlsx
+++ b/deliverables/02-equipment/CFU-000-ME-DS-000_Equipment-Datasheets-Combined.xlsx
@@ -620,7 +620,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>P-101A/B, P-102A/B, P-103A/B, P-104A/B, P-105A/B, P-106A/B, P-107A/B, P-108A/B, P-109A/B, P-110A/B, P-111A/B, P-112A/B, P-114A/B, P-115A/B, P-116A/B, P-117A/B, P-118, P-201A/B, P-202A/B, P-203A/B, P-204A/B, P-205A/B, P-206A/B</t>
+          <t>P-101A/B, P-102A/B, P-103A/B, P-104A/B, P-105A/B, P-106A/B, P-107A/B, P-108A/B, P-109A/B, P-110A/B, P-111A/B, P-112A/B, P-114A/B, P-115A/B, P-116A/B, P-117A/B, P-118, P-119A/B, P-201A/B, P-202A/B, P-203A/B, P-204A/B, P-205A/B, P-206A/B</t>
         </is>
       </c>
     </row>
@@ -637,7 +637,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>PSV-1001, PSV-1002, PSV-1003, PSV-1004, PSV-1005, PSV-1006, PSV-1007, PSV-1008, PSV-1009, PSV-1010, PSV-2001, PSV-2002</t>
+          <t>PSV-1001, PSV-1002, PSV-1003, PSV-1004, PSV-1005, PSV-1006, PSV-1007, PSV-1008, PSV-1009, PSV-1010, PSV-2001, PSV-2002, PSV-1011, PSV-2003, TSV-typ</t>
         </is>
       </c>
     </row>
@@ -14652,57 +14652,57 @@
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>30 / 20 barg</t>
+          <t>35 / 20 barg</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>30 / 20 barg</t>
+          <t>35 / 20 barg</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>30 / 20 barg</t>
+          <t>35 / 20 barg</t>
         </is>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>30 / 20 barg</t>
+          <t>35 / 20 barg</t>
         </is>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>30 / 20 barg</t>
+          <t>35 / 20 barg</t>
         </is>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>30 / 20 barg</t>
+          <t>45 / 20 barg</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
         <is>
-          <t>30 / 20 barg</t>
+          <t>45 / 20 barg</t>
         </is>
       </c>
       <c r="J22" s="10" t="inlineStr">
         <is>
-          <t>30 / 20 barg</t>
+          <t>45 / 20 barg</t>
         </is>
       </c>
       <c r="K22" s="10" t="inlineStr">
         <is>
-          <t>30 / 20 barg</t>
+          <t>45 / 20 barg</t>
         </is>
       </c>
       <c r="L22" s="10" t="inlineStr">
         <is>
-          <t>30 / 20 barg</t>
+          <t>45 / 20 barg</t>
         </is>
       </c>
       <c r="M22" s="10" t="inlineStr">
         <is>
-          <t>30 / 20 barg</t>
+          <t>45 / 20 barg</t>
         </is>
       </c>
       <c r="N22" s="10" t="inlineStr">
@@ -14878,57 +14878,57 @@
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>39.0 / 26.0 barg</t>
+          <t>45.5 / 26.0 barg</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>39.0 / 26.0 barg</t>
+          <t>45.5 / 26.0 barg</t>
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>39.0 / 26.0 barg</t>
+          <t>45.5 / 26.0 barg</t>
         </is>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>39.0 / 26.0 barg</t>
+          <t>45.5 / 26.0 barg</t>
         </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>39.0 / 26.0 barg</t>
+          <t>45.5 / 26.0 barg</t>
         </is>
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>39.0 / 26.0 barg</t>
+          <t>58.5 / 26.0 barg</t>
         </is>
       </c>
       <c r="I24" s="10" t="inlineStr">
         <is>
-          <t>39.0 / 26.0 barg</t>
+          <t>58.5 / 26.0 barg</t>
         </is>
       </c>
       <c r="J24" s="10" t="inlineStr">
         <is>
-          <t>39.0 / 26.0 barg</t>
+          <t>58.5 / 26.0 barg</t>
         </is>
       </c>
       <c r="K24" s="10" t="inlineStr">
         <is>
-          <t>39.0 / 26.0 barg</t>
+          <t>58.5 / 26.0 barg</t>
         </is>
       </c>
       <c r="L24" s="10" t="inlineStr">
         <is>
-          <t>39.0 / 26.0 barg</t>
+          <t>58.5 / 26.0 barg</t>
         </is>
       </c>
       <c r="M24" s="10" t="inlineStr">
         <is>
-          <t>39.0 / 26.0 barg</t>
+          <t>58.5 / 26.0 barg</t>
         </is>
       </c>
       <c r="N24" s="10" t="inlineStr">
@@ -15242,32 +15242,32 @@
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>16" 300#</t>
+          <t>16" 600#</t>
         </is>
       </c>
       <c r="I27" s="10" t="inlineStr">
         <is>
-          <t>16" 300#</t>
+          <t>16" 600#</t>
         </is>
       </c>
       <c r="J27" s="10" t="inlineStr">
         <is>
-          <t>16" 300#</t>
+          <t>16" 600#</t>
         </is>
       </c>
       <c r="K27" s="10" t="inlineStr">
         <is>
-          <t>16" 300#</t>
+          <t>16" 600#</t>
         </is>
       </c>
       <c r="L27" s="10" t="inlineStr">
         <is>
-          <t>16" 300#</t>
+          <t>16" 600#</t>
         </is>
       </c>
       <c r="M27" s="10" t="inlineStr">
         <is>
-          <t>8" 300#</t>
+          <t>8" 600#</t>
         </is>
       </c>
       <c r="N27" s="10" t="inlineStr">
@@ -15782,57 +15782,57 @@
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>SA-516-70 / 1200 mm / 20 mm</t>
+          <t>SA-516-70 / 1200 mm / 22 mm</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>SA-516-70 / 1300 mm / 20 mm</t>
+          <t>SA-516-70 / 1300 mm / 25 mm</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>SA-516-70 / 1250 mm / 20 mm</t>
+          <t>SA-516-70 / 1250 mm / 25 mm</t>
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>SA-516-70 / 1200 mm / 20 mm</t>
+          <t>SA-516-70 / 1200 mm / 22 mm</t>
         </is>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>SA-516-70 / 1300 mm / 22 mm</t>
+          <t>SA-516-70 / 1300 mm / 25 mm</t>
         </is>
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>SA-516-70 / 1350 mm / 22 mm</t>
+          <t>SA-516-70 / 1350 mm / 30 mm</t>
         </is>
       </c>
       <c r="I32" s="10" t="inlineStr">
         <is>
-          <t>SA-516-70 / 1150 mm / 22 mm</t>
+          <t>SA-516-70 / 1150 mm / 30 mm</t>
         </is>
       </c>
       <c r="J32" s="10" t="inlineStr">
         <is>
-          <t>SA-387-11-2 / 1400 mm / 25 mm</t>
+          <t>SA-387-11-2 / 1400 mm / 32 mm</t>
         </is>
       </c>
       <c r="K32" s="10" t="inlineStr">
         <is>
-          <t>SA-387-11-2 / 1000 mm / 20 mm</t>
+          <t>SA-387-11-2 / 1000 mm / 25 mm</t>
         </is>
       </c>
       <c r="L32" s="10" t="inlineStr">
         <is>
-          <t>SA-387-11-2 / 1300 mm / 22 mm</t>
+          <t>SA-387-11-2 / 1300 mm / 32 mm</t>
         </is>
       </c>
       <c r="M32" s="10" t="inlineStr">
         <is>
-          <t>SA-387-11-2 / 1400 mm / 25 mm</t>
+          <t>SA-387-11-2 / 1400 mm / 36 mm</t>
         </is>
       </c>
       <c r="N32" s="10" t="inlineStr">
@@ -16912,57 +16912,57 @@
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>18.9 / 27.2 t</t>
+          <t>19.4 / 27.6 t</t>
         </is>
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>22.4 / 32.0 t</t>
+          <t>23.6 / 33.3 t</t>
         </is>
       </c>
       <c r="E42" s="10" t="inlineStr">
         <is>
-          <t>20.7 / 29.6 t</t>
+          <t>21.9 / 30.8 t</t>
         </is>
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t>19.5 / 27.7 t</t>
+          <t>20.0 / 28.2 t</t>
         </is>
       </c>
       <c r="G42" s="10" t="inlineStr">
         <is>
-          <t>22.7 / 32.3 t</t>
+          <t>23.4 / 33.1 t</t>
         </is>
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
-          <t>25.2 / 35.6 t</t>
+          <t>27.3 / 37.7 t</t>
         </is>
       </c>
       <c r="I42" s="10" t="inlineStr">
         <is>
-          <t>18.2 / 25.8 t</t>
+          <t>20.0 / 27.6 t</t>
         </is>
       </c>
       <c r="J42" s="10" t="inlineStr">
         <is>
-          <t>28.2 / 39.3 t</t>
+          <t>30.1 / 41.2 t</t>
         </is>
       </c>
       <c r="K42" s="10" t="inlineStr">
         <is>
-          <t>14.5 / 20.2 t</t>
+          <t>15.5 / 21.2 t</t>
         </is>
       </c>
       <c r="L42" s="10" t="inlineStr">
         <is>
-          <t>23.2 / 32.9 t</t>
+          <t>25.7 / 35.4 t</t>
         </is>
       </c>
       <c r="M42" s="10" t="inlineStr">
         <is>
-          <t>28.1 / 39.3 t</t>
+          <t>31.1 / 42.3 t</t>
         </is>
       </c>
       <c r="N42" s="10" t="inlineStr">
@@ -19306,7 +19306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y40"/>
+  <dimension ref="A1:Z40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -19334,6 +19334,7 @@
     <col width="22" customWidth="1" min="23" max="23"/>
     <col width="22" customWidth="1" min="24" max="24"/>
     <col width="22" customWidth="1" min="25" max="25"/>
+    <col width="22" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19366,6 +19367,7 @@
       <c r="W1" t="inlineStr"/>
       <c r="X1" t="inlineStr"/>
       <c r="Y1" t="inlineStr"/>
+      <c r="Z1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -19465,30 +19467,35 @@
       </c>
       <c r="T2" s="5" t="inlineStr">
         <is>
+          <t>P-119A/B</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="inlineStr">
+        <is>
           <t>P-201A/B</t>
         </is>
       </c>
-      <c r="U2" s="5" t="inlineStr">
+      <c r="V2" s="5" t="inlineStr">
         <is>
           <t>P-202A/B</t>
         </is>
       </c>
-      <c r="V2" s="5" t="inlineStr">
+      <c r="W2" s="5" t="inlineStr">
         <is>
           <t>P-203A/B</t>
         </is>
       </c>
-      <c r="W2" s="5" t="inlineStr">
+      <c r="X2" s="5" t="inlineStr">
         <is>
           <t>P-204A/B</t>
         </is>
       </c>
-      <c r="X2" s="5" t="inlineStr">
+      <c r="Y2" s="5" t="inlineStr">
         <is>
           <t>P-205A/B</t>
         </is>
       </c>
-      <c r="Y2" s="5" t="inlineStr">
+      <c r="Z2" s="5" t="inlineStr">
         <is>
           <t>P-206A/B</t>
         </is>
@@ -19524,6 +19531,7 @@
       <c r="W3" s="8" t="n"/>
       <c r="X3" s="8" t="n"/>
       <c r="Y3" s="8" t="n"/>
+      <c r="Z3" s="8" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="9" t="inlineStr"/>
@@ -19647,6 +19655,11 @@
           <t>API 610 12th ed. / ISO 13709</t>
         </is>
       </c>
+      <c r="Z4" s="10" t="inlineStr">
+        <is>
+          <t>API 610 12th ed. / ISO 13709</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr"/>
@@ -19742,30 +19755,35 @@
       </c>
       <c r="T5" s="10" t="inlineStr">
         <is>
+          <t>OH2</t>
+        </is>
+      </c>
+      <c r="U5" s="10" t="inlineStr">
+        <is>
           <t>BB2</t>
         </is>
       </c>
-      <c r="U5" s="10" t="inlineStr">
+      <c r="V5" s="10" t="inlineStr">
         <is>
           <t>BB2</t>
         </is>
       </c>
-      <c r="V5" s="10" t="inlineStr">
+      <c r="W5" s="10" t="inlineStr">
         <is>
           <t>BB2</t>
         </is>
       </c>
-      <c r="W5" s="10" t="inlineStr">
+      <c r="X5" s="10" t="inlineStr">
         <is>
           <t>BB2</t>
         </is>
       </c>
-      <c r="X5" s="10" t="inlineStr">
+      <c r="Y5" s="10" t="inlineStr">
         <is>
           <t>OH2</t>
         </is>
       </c>
-      <c r="Y5" s="10" t="inlineStr">
+      <c r="Z5" s="10" t="inlineStr">
         <is>
           <t>API 674/675 PD</t>
         </is>
@@ -19893,6 +19911,11 @@
           <t>2 (1 operating + 1 spare)</t>
         </is>
       </c>
+      <c r="Z6" s="10" t="inlineStr">
+        <is>
+          <t>2 (1 operating + 1 spare)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr"/>
@@ -19988,30 +20011,35 @@
       </c>
       <c r="T7" s="10" t="inlineStr">
         <is>
+          <t>Flare KO drum pump-out</t>
+        </is>
+      </c>
+      <c r="U7" s="10" t="inlineStr">
+        <is>
           <t>LVGO pumparound / product</t>
         </is>
       </c>
-      <c r="U7" s="10" t="inlineStr">
+      <c r="V7" s="10" t="inlineStr">
         <is>
           <t>HVGO pumparound / product</t>
         </is>
       </c>
-      <c r="V7" s="10" t="inlineStr">
+      <c r="W7" s="10" t="inlineStr">
         <is>
           <t>Slop wax</t>
         </is>
       </c>
-      <c r="W7" s="10" t="inlineStr">
+      <c r="X7" s="10" t="inlineStr">
         <is>
           <t>Vacuum residue (incl. quench)</t>
         </is>
       </c>
-      <c r="X7" s="10" t="inlineStr">
+      <c r="Y7" s="10" t="inlineStr">
         <is>
           <t>Hotwell sour water</t>
         </is>
       </c>
-      <c r="Y7" s="10" t="inlineStr">
+      <c r="Z7" s="10" t="inlineStr">
         <is>
           <t>Hotwell slop oil</t>
         </is>
@@ -20139,6 +20167,11 @@
           <t>Electric motor</t>
         </is>
       </c>
+      <c r="Z8" s="10" t="inlineStr">
+        <is>
+          <t>Electric motor</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr"/>
@@ -20234,30 +20267,35 @@
       </c>
       <c r="T9" s="10" t="inlineStr">
         <is>
+          <t>D-104 flare KO drum (liquid at bubble point, 0.2 barg)</t>
+        </is>
+      </c>
+      <c r="U9" s="10" t="inlineStr">
+        <is>
           <t>C-201 LVGO collector</t>
         </is>
       </c>
-      <c r="U9" s="10" t="inlineStr">
+      <c r="V9" s="10" t="inlineStr">
         <is>
           <t>C-201 HVGO collector</t>
         </is>
       </c>
-      <c r="V9" s="10" t="inlineStr">
+      <c r="W9" s="10" t="inlineStr">
         <is>
           <t>C-201 slop wax collector</t>
         </is>
       </c>
-      <c r="W9" s="10" t="inlineStr">
+      <c r="X9" s="10" t="inlineStr">
         <is>
           <t>C-201 boot (quenched VR)</t>
         </is>
       </c>
-      <c r="X9" s="10" t="inlineStr">
+      <c r="Y9" s="10" t="inlineStr">
         <is>
           <t>D-201 hotwell water compartment</t>
         </is>
       </c>
-      <c r="Y9" s="10" t="inlineStr">
+      <c r="Z9" s="10" t="inlineStr">
         <is>
           <t>D-201 slop oil compartment</t>
         </is>
@@ -20293,6 +20331,7 @@
       <c r="W10" s="8" t="n"/>
       <c r="X10" s="8" t="n"/>
       <c r="Y10" s="8" t="n"/>
+      <c r="Z10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr"/>
@@ -20388,30 +20427,35 @@
       </c>
       <c r="T11" s="10" t="inlineStr">
         <is>
+          <t>Flare KO drum pump-out</t>
+        </is>
+      </c>
+      <c r="U11" s="10" t="inlineStr">
+        <is>
           <t>LVGO pumparound / product</t>
         </is>
       </c>
-      <c r="U11" s="10" t="inlineStr">
+      <c r="V11" s="10" t="inlineStr">
         <is>
           <t>HVGO pumparound / product</t>
         </is>
       </c>
-      <c r="V11" s="10" t="inlineStr">
+      <c r="W11" s="10" t="inlineStr">
         <is>
           <t>Slop wax</t>
         </is>
       </c>
-      <c r="W11" s="10" t="inlineStr">
+      <c r="X11" s="10" t="inlineStr">
         <is>
           <t>Vacuum residue (incl. quench)</t>
         </is>
       </c>
-      <c r="X11" s="10" t="inlineStr">
+      <c r="Y11" s="10" t="inlineStr">
         <is>
           <t>Hotwell sour water</t>
         </is>
       </c>
-      <c r="Y11" s="10" t="inlineStr">
+      <c r="Z11" s="10" t="inlineStr">
         <is>
           <t>Hotwell slop oil</t>
         </is>
@@ -20511,30 +20555,35 @@
       </c>
       <c r="T12" s="10" t="inlineStr">
         <is>
+          <t>60 / 90 C</t>
+        </is>
+      </c>
+      <c r="U12" s="10" t="inlineStr">
+        <is>
           <t>224 / 255 C</t>
         </is>
       </c>
-      <c r="U12" s="10" t="inlineStr">
+      <c r="V12" s="10" t="inlineStr">
         <is>
           <t>315 / 345 C</t>
         </is>
       </c>
-      <c r="V12" s="10" t="inlineStr">
+      <c r="W12" s="10" t="inlineStr">
         <is>
           <t>378 / 410 C</t>
         </is>
       </c>
-      <c r="W12" s="10" t="inlineStr">
+      <c r="X12" s="10" t="inlineStr">
         <is>
           <t>366 / 395 C</t>
         </is>
       </c>
-      <c r="X12" s="10" t="inlineStr">
+      <c r="Y12" s="10" t="inlineStr">
         <is>
           <t>45 / 75 C</t>
         </is>
       </c>
-      <c r="Y12" s="10" t="inlineStr">
+      <c r="Z12" s="10" t="inlineStr">
         <is>
           <t>45 / 75 C</t>
         </is>
@@ -20634,30 +20683,35 @@
       </c>
       <c r="T13" s="10" t="inlineStr">
         <is>
+          <t>800 kg/m3</t>
+        </is>
+      </c>
+      <c r="U13" s="10" t="inlineStr">
+        <is>
           <t>737 kg/m3</t>
         </is>
       </c>
-      <c r="U13" s="10" t="inlineStr">
+      <c r="V13" s="10" t="inlineStr">
         <is>
           <t>709 kg/m3</t>
         </is>
       </c>
-      <c r="V13" s="10" t="inlineStr">
+      <c r="W13" s="10" t="inlineStr">
         <is>
           <t>714 kg/m3</t>
         </is>
       </c>
-      <c r="W13" s="10" t="inlineStr">
+      <c r="X13" s="10" t="inlineStr">
         <is>
           <t>761 kg/m3</t>
         </is>
       </c>
-      <c r="X13" s="10" t="inlineStr">
+      <c r="Y13" s="10" t="inlineStr">
         <is>
           <t>990 kg/m3</t>
         </is>
       </c>
-      <c r="Y13" s="10" t="inlineStr">
+      <c r="Z13" s="10" t="inlineStr">
         <is>
           <t>850 kg/m3</t>
         </is>
@@ -20785,6 +20839,11 @@
           <t>TBD (process)</t>
         </is>
       </c>
+      <c r="Z14" s="10" t="inlineStr">
+        <is>
+          <t>TBD (process)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr"/>
@@ -20880,30 +20939,35 @@
       </c>
       <c r="T15" s="10" t="inlineStr">
         <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+      <c r="U15" s="10" t="inlineStr">
+        <is>
           <t>Bubble point (= surface P)</t>
         </is>
       </c>
-      <c r="U15" s="10" t="inlineStr">
+      <c r="V15" s="10" t="inlineStr">
         <is>
           <t>Bubble point (= surface P)</t>
         </is>
       </c>
-      <c r="V15" s="10" t="inlineStr">
+      <c r="W15" s="10" t="inlineStr">
         <is>
           <t>Bubble point (= surface P)</t>
         </is>
       </c>
-      <c r="W15" s="10" t="inlineStr">
+      <c r="X15" s="10" t="inlineStr">
         <is>
           <t>Bubble point (= surface P)</t>
         </is>
       </c>
-      <c r="X15" s="10" t="inlineStr">
+      <c r="Y15" s="10" t="inlineStr">
         <is>
           <t>Water</t>
         </is>
       </c>
-      <c r="Y15" s="10" t="inlineStr">
+      <c r="Z15" s="10" t="inlineStr">
         <is>
           <t>Estimated</t>
         </is>
@@ -21003,30 +21067,35 @@
       </c>
       <c r="T16" s="10" t="inlineStr">
         <is>
+          <t>20.6 / 18.8 m3/h</t>
+        </is>
+      </c>
+      <c r="U16" s="10" t="inlineStr">
+        <is>
           <t>198.3 / 180.3 m3/h</t>
         </is>
       </c>
-      <c r="U16" s="10" t="inlineStr">
+      <c r="V16" s="10" t="inlineStr">
         <is>
           <t>391.0 / 355.4 m3/h</t>
         </is>
       </c>
-      <c r="V16" s="10" t="inlineStr">
+      <c r="W16" s="10" t="inlineStr">
         <is>
           <t>12.2 / 11.1 m3/h</t>
         </is>
       </c>
-      <c r="W16" s="10" t="inlineStr">
+      <c r="X16" s="10" t="inlineStr">
         <is>
           <t>195.6 / 177.8 m3/h</t>
         </is>
       </c>
-      <c r="X16" s="10" t="inlineStr">
+      <c r="Y16" s="10" t="inlineStr">
         <is>
           <t>13.5 / 12.3 m3/h</t>
         </is>
       </c>
-      <c r="Y16" s="10" t="inlineStr">
+      <c r="Z16" s="10" t="inlineStr">
         <is>
           <t>0.6 / 0.6 m3/h</t>
         </is>
@@ -21126,30 +21195,35 @@
       </c>
       <c r="T17" s="10" t="inlineStr">
         <is>
+          <t>0.19 barg</t>
+        </is>
+      </c>
+      <c r="U17" s="10" t="inlineStr">
+        <is>
           <t>1.60 barg</t>
         </is>
       </c>
-      <c r="U17" s="10" t="inlineStr">
+      <c r="V17" s="10" t="inlineStr">
         <is>
           <t>0.98 barg</t>
         </is>
       </c>
-      <c r="V17" s="10" t="inlineStr">
+      <c r="W17" s="10" t="inlineStr">
         <is>
           <t>0.45 barg</t>
         </is>
       </c>
-      <c r="W17" s="10" t="inlineStr">
+      <c r="X17" s="10" t="inlineStr">
         <is>
           <t>-0.55 barg</t>
         </is>
       </c>
-      <c r="X17" s="10" t="inlineStr">
+      <c r="Y17" s="10" t="inlineStr">
         <is>
           <t>-0.02 barg</t>
         </is>
       </c>
-      <c r="Y17" s="10" t="inlineStr">
+      <c r="Z17" s="10" t="inlineStr">
         <is>
           <t>-0.01 barg</t>
         </is>
@@ -21224,7 +21298,7 @@
       </c>
       <c r="O18" s="10" t="inlineStr">
         <is>
-          <t>8.93 barg</t>
+          <t>14.93 barg</t>
         </is>
       </c>
       <c r="P18" s="10" t="inlineStr">
@@ -21249,30 +21323,35 @@
       </c>
       <c r="T18" s="10" t="inlineStr">
         <is>
+          <t>6.19 barg</t>
+        </is>
+      </c>
+      <c r="U18" s="10" t="inlineStr">
+        <is>
           <t>11.60 barg</t>
         </is>
       </c>
-      <c r="U18" s="10" t="inlineStr">
+      <c r="V18" s="10" t="inlineStr">
         <is>
           <t>10.98 barg</t>
         </is>
       </c>
-      <c r="V18" s="10" t="inlineStr">
+      <c r="W18" s="10" t="inlineStr">
         <is>
           <t>8.45 barg</t>
         </is>
       </c>
-      <c r="W18" s="10" t="inlineStr">
+      <c r="X18" s="10" t="inlineStr">
         <is>
           <t>13.45 barg</t>
         </is>
       </c>
-      <c r="X18" s="10" t="inlineStr">
+      <c r="Y18" s="10" t="inlineStr">
         <is>
           <t>4.98 barg</t>
         </is>
       </c>
-      <c r="Y18" s="10" t="inlineStr">
+      <c r="Z18" s="10" t="inlineStr">
         <is>
           <t>4.99 barg</t>
         </is>
@@ -21347,7 +21426,7 @@
       </c>
       <c r="O19" s="10" t="inlineStr">
         <is>
-          <t>8.0 bar / 82 m</t>
+          <t>14.0 bar / 144 m</t>
         </is>
       </c>
       <c r="P19" s="10" t="inlineStr">
@@ -21372,30 +21451,35 @@
       </c>
       <c r="T19" s="10" t="inlineStr">
         <is>
+          <t>6.0 bar / 76 m</t>
+        </is>
+      </c>
+      <c r="U19" s="10" t="inlineStr">
+        <is>
           <t>10.0 bar / 138 m</t>
         </is>
       </c>
-      <c r="U19" s="10" t="inlineStr">
+      <c r="V19" s="10" t="inlineStr">
         <is>
           <t>10.0 bar / 144 m</t>
         </is>
       </c>
-      <c r="V19" s="10" t="inlineStr">
+      <c r="W19" s="10" t="inlineStr">
         <is>
           <t>8.0 bar / 114 m</t>
         </is>
       </c>
-      <c r="W19" s="10" t="inlineStr">
+      <c r="X19" s="10" t="inlineStr">
         <is>
           <t>14.0 bar / 187 m</t>
         </is>
       </c>
-      <c r="X19" s="10" t="inlineStr">
+      <c r="Y19" s="10" t="inlineStr">
         <is>
           <t>5.0 bar / 51 m</t>
         </is>
       </c>
-      <c r="Y19" s="10" t="inlineStr">
+      <c r="Z19" s="10" t="inlineStr">
         <is>
           <t>5.0 bar / 60 m</t>
         </is>
@@ -21495,30 +21579,35 @@
       </c>
       <c r="T20" s="10" t="inlineStr">
         <is>
+          <t>-0.1 m</t>
+        </is>
+      </c>
+      <c r="U20" s="10" t="inlineStr">
+        <is>
           <t>35.7 m</t>
         </is>
       </c>
-      <c r="U20" s="10" t="inlineStr">
+      <c r="V20" s="10" t="inlineStr">
         <is>
           <t>28.1 m</t>
         </is>
       </c>
-      <c r="V20" s="10" t="inlineStr">
+      <c r="W20" s="10" t="inlineStr">
         <is>
           <t>20.0 m</t>
         </is>
       </c>
-      <c r="W20" s="10" t="inlineStr">
+      <c r="X20" s="10" t="inlineStr">
         <is>
           <t>5.2 m</t>
         </is>
       </c>
-      <c r="X20" s="10" t="inlineStr">
+      <c r="Y20" s="10" t="inlineStr">
         <is>
           <t>9.3 m</t>
         </is>
       </c>
-      <c r="Y20" s="10" t="inlineStr">
+      <c r="Z20" s="10" t="inlineStr">
         <is>
           <t>11.4 m</t>
         </is>
@@ -21618,30 +21707,35 @@
       </c>
       <c r="T21" s="10" t="inlineStr">
         <is>
+          <t>0.6 m</t>
+        </is>
+      </c>
+      <c r="U21" s="10" t="inlineStr">
+        <is>
           <t>2.7 m</t>
         </is>
       </c>
-      <c r="U21" s="10" t="inlineStr">
+      <c r="V21" s="10" t="inlineStr">
         <is>
           <t>4.2 m</t>
         </is>
       </c>
-      <c r="V21" s="10" t="inlineStr">
+      <c r="W21" s="10" t="inlineStr">
         <is>
           <t>1.0 m</t>
         </is>
       </c>
-      <c r="W21" s="10" t="inlineStr">
+      <c r="X21" s="10" t="inlineStr">
         <is>
           <t>2.6 m</t>
         </is>
       </c>
-      <c r="X21" s="10" t="inlineStr">
+      <c r="Y21" s="10" t="inlineStr">
         <is>
           <t>1.1 m</t>
         </is>
       </c>
-      <c r="Y21" s="10" t="inlineStr">
+      <c r="Z21" s="10" t="inlineStr">
         <is>
           <t>0.1 m</t>
         </is>
@@ -21741,30 +21835,35 @@
       </c>
       <c r="T22" s="10" t="inlineStr">
         <is>
+          <t>-0.7 m</t>
+        </is>
+      </c>
+      <c r="U22" s="10" t="inlineStr">
+        <is>
           <t>33.0 m</t>
         </is>
       </c>
-      <c r="U22" s="10" t="inlineStr">
+      <c r="V22" s="10" t="inlineStr">
         <is>
           <t>23.9 m</t>
         </is>
       </c>
-      <c r="V22" s="10" t="inlineStr">
+      <c r="W22" s="10" t="inlineStr">
         <is>
           <t>19.0 m</t>
         </is>
       </c>
-      <c r="W22" s="10" t="inlineStr">
+      <c r="X22" s="10" t="inlineStr">
         <is>
           <t>2.6 m</t>
         </is>
       </c>
-      <c r="X22" s="10" t="inlineStr">
+      <c r="Y22" s="10" t="inlineStr">
         <is>
           <t>8.1 m</t>
         </is>
       </c>
-      <c r="Y22" s="10" t="inlineStr">
+      <c r="Z22" s="10" t="inlineStr">
         <is>
           <t>11.3 m</t>
         </is>
@@ -21839,7 +21938,7 @@
       </c>
       <c r="O23" s="10" t="inlineStr">
         <is>
-          <t>8.2 kW</t>
+          <t>14.3 kW</t>
         </is>
       </c>
       <c r="P23" s="10" t="inlineStr">
@@ -21864,30 +21963,35 @@
       </c>
       <c r="T23" s="10" t="inlineStr">
         <is>
+          <t>3.4 kW</t>
+        </is>
+      </c>
+      <c r="U23" s="10" t="inlineStr">
+        <is>
           <t>55.1 kW</t>
         </is>
       </c>
-      <c r="U23" s="10" t="inlineStr">
+      <c r="V23" s="10" t="inlineStr">
         <is>
           <t>108.6 kW</t>
         </is>
       </c>
-      <c r="V23" s="10" t="inlineStr">
+      <c r="W23" s="10" t="inlineStr">
         <is>
           <t>2.7 kW</t>
         </is>
       </c>
-      <c r="W23" s="10" t="inlineStr">
+      <c r="X23" s="10" t="inlineStr">
         <is>
           <t>76.1 kW</t>
         </is>
       </c>
-      <c r="X23" s="10" t="inlineStr">
+      <c r="Y23" s="10" t="inlineStr">
         <is>
           <t>1.9 kW</t>
         </is>
       </c>
-      <c r="Y23" s="10" t="inlineStr">
+      <c r="Z23" s="10" t="inlineStr">
         <is>
           <t>0.1 kW</t>
         </is>
@@ -21987,30 +22091,35 @@
       </c>
       <c r="T24" s="10" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U24" s="10" t="inlineStr">
+        <is>
           <t>Sour (H2S) / naphthenic</t>
         </is>
       </c>
-      <c r="U24" s="10" t="inlineStr">
+      <c r="V24" s="10" t="inlineStr">
         <is>
           <t>Sour (H2S) / naphthenic</t>
         </is>
       </c>
-      <c r="V24" s="10" t="inlineStr">
+      <c r="W24" s="10" t="inlineStr">
         <is>
           <t>Sour (H2S) / naphthenic</t>
         </is>
       </c>
-      <c r="W24" s="10" t="inlineStr">
+      <c r="X24" s="10" t="inlineStr">
         <is>
           <t>Sour (H2S) / naphthenic</t>
         </is>
       </c>
-      <c r="X24" s="10" t="inlineStr">
+      <c r="Y24" s="10" t="inlineStr">
         <is>
           <t>Sour</t>
         </is>
       </c>
-      <c r="Y24" s="10" t="inlineStr">
+      <c r="Z24" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -22046,6 +22155,7 @@
       <c r="W25" s="8" t="n"/>
       <c r="X25" s="8" t="n"/>
       <c r="Y25" s="8" t="n"/>
+      <c r="Z25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr"/>
@@ -22151,20 +22261,25 @@
       </c>
       <c r="V26" s="10" t="inlineStr">
         <is>
+          <t>1780 rpm</t>
+        </is>
+      </c>
+      <c r="W26" s="10" t="inlineStr">
+        <is>
           <t>3560 rpm</t>
         </is>
       </c>
-      <c r="W26" s="10" t="inlineStr">
+      <c r="X26" s="10" t="inlineStr">
         <is>
           <t>1780 rpm</t>
         </is>
       </c>
-      <c r="X26" s="10" t="inlineStr">
+      <c r="Y26" s="10" t="inlineStr">
         <is>
           <t>3560 rpm</t>
         </is>
       </c>
-      <c r="Y26" s="10" t="inlineStr">
+      <c r="Z26" s="10" t="inlineStr">
         <is>
           <t>3560 rpm</t>
         </is>
@@ -22279,15 +22394,20 @@
       </c>
       <c r="W27" s="10" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X27" s="10" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="X27" s="10" t="inlineStr">
+      <c r="Y27" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y27" s="10" t="inlineStr">
+      <c r="Z27" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -22387,30 +22507,35 @@
       </c>
       <c r="T28" s="10" t="inlineStr">
         <is>
+          <t>60 %</t>
+        </is>
+      </c>
+      <c r="U28" s="10" t="inlineStr">
+        <is>
           <t>68 %</t>
         </is>
       </c>
-      <c r="U28" s="10" t="inlineStr">
+      <c r="V28" s="10" t="inlineStr">
         <is>
           <t>70 %</t>
         </is>
       </c>
-      <c r="V28" s="10" t="inlineStr">
+      <c r="W28" s="10" t="inlineStr">
         <is>
           <t>58 %</t>
         </is>
       </c>
-      <c r="W28" s="10" t="inlineStr">
+      <c r="X28" s="10" t="inlineStr">
         <is>
           <t>68 %</t>
         </is>
       </c>
-      <c r="X28" s="10" t="inlineStr">
+      <c r="Y28" s="10" t="inlineStr">
         <is>
           <t>58 %</t>
         </is>
       </c>
-      <c r="Y28" s="10" t="inlineStr">
+      <c r="Z28" s="10" t="inlineStr">
         <is>
           <t>55 %</t>
         </is>
@@ -22485,7 +22610,7 @@
       </c>
       <c r="O29" s="10" t="inlineStr">
         <is>
-          <t>13.2 kW</t>
+          <t>23.1 kW</t>
         </is>
       </c>
       <c r="P29" s="10" t="inlineStr">
@@ -22510,30 +22635,35 @@
       </c>
       <c r="T29" s="10" t="inlineStr">
         <is>
+          <t>5.7 kW</t>
+        </is>
+      </c>
+      <c r="U29" s="10" t="inlineStr">
+        <is>
           <t>81.3 kW</t>
         </is>
       </c>
-      <c r="U29" s="10" t="inlineStr">
+      <c r="V29" s="10" t="inlineStr">
         <is>
           <t>154.8 kW</t>
         </is>
       </c>
-      <c r="V29" s="10" t="inlineStr">
+      <c r="W29" s="10" t="inlineStr">
         <is>
           <t>4.7 kW</t>
         </is>
       </c>
-      <c r="W29" s="10" t="inlineStr">
+      <c r="X29" s="10" t="inlineStr">
         <is>
           <t>112.3 kW</t>
         </is>
       </c>
-      <c r="X29" s="10" t="inlineStr">
+      <c r="Y29" s="10" t="inlineStr">
         <is>
           <t>3.2 kW</t>
         </is>
       </c>
-      <c r="Y29" s="10" t="inlineStr">
+      <c r="Z29" s="10" t="inlineStr">
         <is>
           <t>0.2 kW</t>
         </is>
@@ -22608,14 +22738,14 @@
       </c>
       <c r="O30" s="10" t="inlineStr">
         <is>
+          <t>30 kW</t>
+        </is>
+      </c>
+      <c r="P30" s="10" t="inlineStr">
+        <is>
           <t>18.5 kW</t>
         </is>
       </c>
-      <c r="P30" s="10" t="inlineStr">
-        <is>
-          <t>18.5 kW</t>
-        </is>
-      </c>
       <c r="Q30" s="10" t="inlineStr">
         <is>
           <t>55 kW</t>
@@ -22633,30 +22763,35 @@
       </c>
       <c r="T30" s="10" t="inlineStr">
         <is>
+          <t>7.5 kW</t>
+        </is>
+      </c>
+      <c r="U30" s="10" t="inlineStr">
+        <is>
           <t>110 kW</t>
         </is>
       </c>
-      <c r="U30" s="10" t="inlineStr">
+      <c r="V30" s="10" t="inlineStr">
         <is>
           <t>200 kW</t>
         </is>
       </c>
-      <c r="V30" s="10" t="inlineStr">
+      <c r="W30" s="10" t="inlineStr">
         <is>
           <t>5.5 kW</t>
         </is>
       </c>
-      <c r="W30" s="10" t="inlineStr">
+      <c r="X30" s="10" t="inlineStr">
         <is>
           <t>132 kW</t>
         </is>
       </c>
-      <c r="X30" s="10" t="inlineStr">
+      <c r="Y30" s="10" t="inlineStr">
         <is>
           <t>3.7 kW</t>
         </is>
       </c>
-      <c r="Y30" s="10" t="inlineStr">
+      <c r="Z30" s="10" t="inlineStr">
         <is>
           <t>0.75 kW</t>
         </is>
@@ -22761,25 +22896,30 @@
       </c>
       <c r="U31" s="10" t="inlineStr">
         <is>
+          <t>480 V, 3 ph, 60 Hz</t>
+        </is>
+      </c>
+      <c r="V31" s="10" t="inlineStr">
+        <is>
           <t>4.16 kV, 3 ph, 60 Hz</t>
         </is>
       </c>
-      <c r="V31" s="10" t="inlineStr">
+      <c r="W31" s="10" t="inlineStr">
         <is>
           <t>480 V, 3 ph, 60 Hz</t>
         </is>
       </c>
-      <c r="W31" s="10" t="inlineStr">
+      <c r="X31" s="10" t="inlineStr">
         <is>
           <t>480 V, 3 ph, 60 Hz</t>
         </is>
       </c>
-      <c r="X31" s="10" t="inlineStr">
+      <c r="Y31" s="10" t="inlineStr">
         <is>
           <t>480 V, 3 ph, 60 Hz</t>
         </is>
       </c>
-      <c r="Y31" s="10" t="inlineStr">
+      <c r="Z31" s="10" t="inlineStr">
         <is>
           <t>480 V, 3 ph, 60 Hz</t>
         </is>
@@ -22907,6 +23047,11 @@
           <t>TEFC, Class I Div 2 Gr D / Zone 2 IIA T3</t>
         </is>
       </c>
+      <c r="Z32" s="10" t="inlineStr">
+        <is>
+          <t>TEFC, Class I Div 2 Gr D / Zone 2 IIA T3</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="9" t="inlineStr"/>
@@ -23002,30 +23147,35 @@
       </c>
       <c r="T33" s="10" t="inlineStr">
         <is>
+          <t>3" / 2" 300# RF (vendor)</t>
+        </is>
+      </c>
+      <c r="U33" s="10" t="inlineStr">
+        <is>
           <t>8" / 6" 300# RF (vendor)</t>
         </is>
       </c>
-      <c r="U33" s="10" t="inlineStr">
+      <c r="V33" s="10" t="inlineStr">
         <is>
           <t>10" / 8" 300# RF (vendor)</t>
         </is>
       </c>
-      <c r="V33" s="10" t="inlineStr">
+      <c r="W33" s="10" t="inlineStr">
         <is>
           <t>2" / 2" 300# RF (vendor)</t>
         </is>
       </c>
-      <c r="W33" s="10" t="inlineStr">
+      <c r="X33" s="10" t="inlineStr">
         <is>
           <t>8" / 6" 300# RF (vendor)</t>
         </is>
       </c>
-      <c r="X33" s="10" t="inlineStr">
+      <c r="Y33" s="10" t="inlineStr">
         <is>
           <t>2" / 2" 300# RF (vendor)</t>
         </is>
       </c>
-      <c r="Y33" s="10" t="inlineStr">
+      <c r="Z33" s="10" t="inlineStr">
         <is>
           <t>2" / 2" 300# RF (vendor)</t>
         </is>
@@ -23153,6 +23303,11 @@
           <t>40 barg (incl. shut-off, TBD)</t>
         </is>
       </c>
+      <c r="Z34" s="10" t="inlineStr">
+        <is>
+          <t>40 barg (incl. shut-off, TBD)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="9" t="inlineStr"/>
@@ -23253,25 +23408,30 @@
       </c>
       <c r="U35" s="10" t="inlineStr">
         <is>
+          <t>S-6 (CS/12Cr)</t>
+        </is>
+      </c>
+      <c r="V35" s="10" t="inlineStr">
+        <is>
           <t>A-8 (316)</t>
         </is>
       </c>
-      <c r="V35" s="10" t="inlineStr">
+      <c r="W35" s="10" t="inlineStr">
         <is>
           <t>A-8 (316)</t>
         </is>
       </c>
-      <c r="W35" s="10" t="inlineStr">
+      <c r="X35" s="10" t="inlineStr">
         <is>
           <t>A-8 (316)</t>
         </is>
       </c>
-      <c r="X35" s="10" t="inlineStr">
+      <c r="Y35" s="10" t="inlineStr">
         <is>
           <t>S-6 (CS/12Cr)</t>
         </is>
       </c>
-      <c r="Y35" s="10" t="inlineStr">
+      <c r="Z35" s="10" t="inlineStr">
         <is>
           <t>S-6 (CS/12Cr)</t>
         </is>
@@ -23376,25 +23536,30 @@
       </c>
       <c r="U36" s="10" t="inlineStr">
         <is>
+          <t>API 682 Plan 11/52, API 682 Cat 2, Arr. 1</t>
+        </is>
+      </c>
+      <c r="V36" s="10" t="inlineStr">
+        <is>
           <t>API 682 Plan 53B, API 682 Cat 2, Arr. 2</t>
         </is>
       </c>
-      <c r="V36" s="10" t="inlineStr">
+      <c r="W36" s="10" t="inlineStr">
         <is>
           <t>API 682 Plan 53B, API 682 Cat 2, Arr. 2</t>
         </is>
       </c>
-      <c r="W36" s="10" t="inlineStr">
+      <c r="X36" s="10" t="inlineStr">
         <is>
           <t>API 682 Plan 53B, API 682 Cat 2, Arr. 2</t>
         </is>
       </c>
-      <c r="X36" s="10" t="inlineStr">
+      <c r="Y36" s="10" t="inlineStr">
         <is>
           <t>API 682 Plan 11/52, API 682 Cat 2, Arr. 1</t>
         </is>
       </c>
-      <c r="Y36" s="10" t="inlineStr">
+      <c r="Z36" s="10" t="inlineStr">
         <is>
           <t>API 682 Plan 11/52, API 682 Cat 2, Arr. 1</t>
         </is>
@@ -23522,6 +23687,11 @@
           <t>Rolling / ring oil</t>
         </is>
       </c>
+      <c r="Z37" s="10" t="inlineStr">
+        <is>
+          <t>Rolling / ring oil</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="9" t="inlineStr"/>
@@ -23645,6 +23815,11 @@
           <t>Flexible disc spacer / API 610 grouted</t>
         </is>
       </c>
+      <c r="Z38" s="10" t="inlineStr">
+        <is>
+          <t>Flexible disc spacer / API 610 grouted</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="9" t="inlineStr"/>
@@ -23768,6 +23943,11 @@
           <t>Vendor (min. flow bypass if &lt; 30 % rated)</t>
         </is>
       </c>
+      <c r="Z39" s="10" t="inlineStr">
+        <is>
+          <t>Vendor (min. flow bypass if &lt; 30 % rated)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="9" t="inlineStr"/>
@@ -23838,14 +24018,14 @@
       </c>
       <c r="O40" s="10" t="inlineStr">
         <is>
+          <t>0.7 t each</t>
+        </is>
+      </c>
+      <c r="P40" s="10" t="inlineStr">
+        <is>
           <t>0.5 t each</t>
         </is>
       </c>
-      <c r="P40" s="10" t="inlineStr">
-        <is>
-          <t>0.5 t each</t>
-        </is>
-      </c>
       <c r="Q40" s="10" t="inlineStr">
         <is>
           <t>1.0 t each</t>
@@ -23863,30 +24043,35 @@
       </c>
       <c r="T40" s="10" t="inlineStr">
         <is>
+          <t>0.4 t each</t>
+        </is>
+      </c>
+      <c r="U40" s="10" t="inlineStr">
+        <is>
           <t>2.7 t each</t>
         </is>
       </c>
-      <c r="U40" s="10" t="inlineStr">
+      <c r="V40" s="10" t="inlineStr">
         <is>
           <t>4.2 t each</t>
         </is>
       </c>
-      <c r="V40" s="10" t="inlineStr">
+      <c r="W40" s="10" t="inlineStr">
         <is>
           <t>0.9 t each</t>
         </is>
       </c>
-      <c r="W40" s="10" t="inlineStr">
+      <c r="X40" s="10" t="inlineStr">
         <is>
           <t>3.0 t each</t>
         </is>
       </c>
-      <c r="X40" s="10" t="inlineStr">
+      <c r="Y40" s="10" t="inlineStr">
         <is>
           <t>0.3 t each</t>
         </is>
       </c>
-      <c r="Y40" s="10" t="inlineStr">
+      <c r="Z40" s="10" t="inlineStr">
         <is>
           <t>0.3 t each</t>
         </is>
@@ -23903,7 +24088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:Q35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -23920,6 +24105,9 @@
     <col width="22" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -23941,6 +24129,9 @@
       <c r="L1" t="inlineStr"/>
       <c r="M1" t="inlineStr"/>
       <c r="N1" t="inlineStr"/>
+      <c r="O1" t="inlineStr"/>
+      <c r="P1" t="inlineStr"/>
+      <c r="Q1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -24011,6 +24202,21 @@
       <c r="N2" s="5" t="inlineStr">
         <is>
           <t>PSV-2002</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>PSV-1011</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr">
+        <is>
+          <t>PSV-2003</t>
+        </is>
+      </c>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>TSV-typ</t>
         </is>
       </c>
     </row>
@@ -24033,6 +24239,9 @@
       <c r="L3" s="8" t="n"/>
       <c r="M3" s="8" t="n"/>
       <c r="N3" s="8" t="n"/>
+      <c r="O3" s="8" t="n"/>
+      <c r="P3" s="8" t="n"/>
+      <c r="Q3" s="8" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="9" t="inlineStr"/>
@@ -24101,6 +24310,21 @@
           <t>PSV-2002 / 1</t>
         </is>
       </c>
+      <c r="O4" s="10" t="inlineStr">
+        <is>
+          <t>PSV-1011 / 1</t>
+        </is>
+      </c>
+      <c r="P4" s="10" t="inlineStr">
+        <is>
+          <t>PSV-2003 / 1</t>
+        </is>
+      </c>
+      <c r="Q4" s="10" t="inlineStr">
+        <is>
+          <t>TSV-typ / 1</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr"/>
@@ -24169,6 +24393,21 @@
           <t>D-201</t>
         </is>
       </c>
+      <c r="O5" s="10" t="inlineStr">
+        <is>
+          <t>E-113 (steam side)</t>
+        </is>
+      </c>
+      <c r="P5" s="10" t="inlineStr">
+        <is>
+          <t>E-201 (steam side)</t>
+        </is>
+      </c>
+      <c r="Q5" s="10" t="inlineStr">
+        <is>
+          <t>CW sides E-115, E-202..E-204</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr"/>
@@ -24237,6 +24476,21 @@
           <t>Fire</t>
         </is>
       </c>
+      <c r="O6" s="10" t="inlineStr">
+        <is>
+          <t>Blocked MP steam outlet (max. generation)</t>
+        </is>
+      </c>
+      <c r="P6" s="10" t="inlineStr">
+        <is>
+          <t>Blocked LP steam outlet (max. generation)</t>
+        </is>
+      </c>
+      <c r="Q6" s="10" t="inlineStr">
+        <is>
+          <t>Thermal expansion (blocked-in CW)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr"/>
@@ -24305,6 +24559,21 @@
           <t>Spring-loaded, full-nozzle, high-lift</t>
         </is>
       </c>
+      <c r="O7" s="10" t="inlineStr">
+        <is>
+          <t>Spring-loaded, full-nozzle, high-lift</t>
+        </is>
+      </c>
+      <c r="P7" s="10" t="inlineStr">
+        <is>
+          <t>Spring-loaded, full-nozzle, high-lift</t>
+        </is>
+      </c>
+      <c r="Q7" s="10" t="inlineStr">
+        <is>
+          <t>Spring-loaded, full-nozzle, high-lift</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr"/>
@@ -24373,6 +24642,21 @@
           <t>Balanced bellows</t>
         </is>
       </c>
+      <c r="O8" s="10" t="inlineStr">
+        <is>
+          <t>Conventional</t>
+        </is>
+      </c>
+      <c r="P8" s="10" t="inlineStr">
+        <is>
+          <t>Conventional</t>
+        </is>
+      </c>
+      <c r="Q8" s="10" t="inlineStr">
+        <is>
+          <t>Conventional</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr"/>
@@ -24441,6 +24725,21 @@
           <t>Flare</t>
         </is>
       </c>
+      <c r="O9" s="10" t="inlineStr">
+        <is>
+          <t>Atmosphere (safe location)</t>
+        </is>
+      </c>
+      <c r="P9" s="10" t="inlineStr">
+        <is>
+          <t>Atmosphere (safe location)</t>
+        </is>
+      </c>
+      <c r="Q9" s="10" t="inlineStr">
+        <is>
+          <t>Grade</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr"/>
@@ -24509,6 +24808,21 @@
           <t>3K4  (inlet x orifice x outlet)</t>
         </is>
       </c>
+      <c r="O10" s="10" t="inlineStr">
+        <is>
+          <t>3L4  (inlet x orifice x outlet)</t>
+        </is>
+      </c>
+      <c r="P10" s="10" t="inlineStr">
+        <is>
+          <t>3K4  (inlet x orifice x outlet)</t>
+        </is>
+      </c>
+      <c r="Q10" s="10" t="inlineStr">
+        <is>
+          <t>1D2  (inlet x orifice x outlet)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr"/>
@@ -24577,6 +24891,21 @@
           <t>3" 150# RF</t>
         </is>
       </c>
+      <c r="O11" s="10" t="inlineStr">
+        <is>
+          <t>3" 300# RF</t>
+        </is>
+      </c>
+      <c r="P11" s="10" t="inlineStr">
+        <is>
+          <t>3" 150# RF</t>
+        </is>
+      </c>
+      <c r="Q11" s="10" t="inlineStr">
+        <is>
+          <t>1" 150# RF</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr"/>
@@ -24643,6 +24972,21 @@
       <c r="N12" s="10" t="inlineStr">
         <is>
           <t>4" 150# RF</t>
+        </is>
+      </c>
+      <c r="O12" s="10" t="inlineStr">
+        <is>
+          <t>4" 150# RF</t>
+        </is>
+      </c>
+      <c r="P12" s="10" t="inlineStr">
+        <is>
+          <t>4" 150# RF</t>
+        </is>
+      </c>
+      <c r="Q12" s="10" t="inlineStr">
+        <is>
+          <t>2" 150# RF</t>
         </is>
       </c>
     </row>
@@ -24665,6 +25009,9 @@
       <c r="L13" s="8" t="n"/>
       <c r="M13" s="8" t="n"/>
       <c r="N13" s="8" t="n"/>
+      <c r="O13" s="8" t="n"/>
+      <c r="P13" s="8" t="n"/>
+      <c r="Q13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr"/>
@@ -24733,6 +25080,21 @@
           <t>Hydrocarbon vapour</t>
         </is>
       </c>
+      <c r="O14" s="10" t="inlineStr">
+        <is>
+          <t>Steam / vapour</t>
+        </is>
+      </c>
+      <c r="P14" s="10" t="inlineStr">
+        <is>
+          <t>Steam / vapour</t>
+        </is>
+      </c>
+      <c r="Q14" s="10" t="inlineStr">
+        <is>
+          <t>Steam / vapour</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr"/>
@@ -24801,6 +25163,21 @@
           <t>6,324 kg/h</t>
         </is>
       </c>
+      <c r="O15" s="10" t="inlineStr">
+        <is>
+          <t>8,833 kg/h</t>
+        </is>
+      </c>
+      <c r="P15" s="10" t="inlineStr">
+        <is>
+          <t>3,054 kg/h</t>
+        </is>
+      </c>
+      <c r="Q15" s="10" t="inlineStr">
+        <is>
+          <t>50 kg/h</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr"/>
@@ -24869,6 +25246,21 @@
           <t>100.0</t>
         </is>
       </c>
+      <c r="O16" s="10" t="inlineStr">
+        <is>
+          <t>18.0</t>
+        </is>
+      </c>
+      <c r="P16" s="10" t="inlineStr">
+        <is>
+          <t>18.0</t>
+        </is>
+      </c>
+      <c r="Q16" s="10" t="inlineStr">
+        <is>
+          <t>18.0</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr"/>
@@ -24937,6 +25329,21 @@
           <t>120 C</t>
         </is>
       </c>
+      <c r="O17" s="10" t="inlineStr">
+        <is>
+          <t>186 C</t>
+        </is>
+      </c>
+      <c r="P17" s="10" t="inlineStr">
+        <is>
+          <t>148 C</t>
+        </is>
+      </c>
+      <c r="Q17" s="10" t="inlineStr">
+        <is>
+          <t>60 C</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr"/>
@@ -25005,6 +25412,21 @@
           <t>1.10 / 1.0</t>
         </is>
       </c>
+      <c r="O18" s="10" t="inlineStr">
+        <is>
+          <t>1.10 / 1.0</t>
+        </is>
+      </c>
+      <c r="P18" s="10" t="inlineStr">
+        <is>
+          <t>1.10 / 1.0</t>
+        </is>
+      </c>
+      <c r="Q18" s="10" t="inlineStr">
+        <is>
+          <t>1.10 / 1.0</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr"/>
@@ -25073,6 +25495,21 @@
           <t>3.5 barg</t>
         </is>
       </c>
+      <c r="O19" s="10" t="inlineStr">
+        <is>
+          <t>12.0 barg</t>
+        </is>
+      </c>
+      <c r="P19" s="10" t="inlineStr">
+        <is>
+          <t>5.0 barg</t>
+        </is>
+      </c>
+      <c r="Q19" s="10" t="inlineStr">
+        <is>
+          <t>7.0 barg</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr"/>
@@ -25141,6 +25578,21 @@
           <t>21 % (fire)</t>
         </is>
       </c>
+      <c r="O20" s="10" t="inlineStr">
+        <is>
+          <t>10 %</t>
+        </is>
+      </c>
+      <c r="P20" s="10" t="inlineStr">
+        <is>
+          <t>10 %</t>
+        </is>
+      </c>
+      <c r="Q20" s="10" t="inlineStr">
+        <is>
+          <t>10 %</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr"/>
@@ -25209,6 +25661,21 @@
           <t>0.5 barg superimposed (var.) + 10 % built-up</t>
         </is>
       </c>
+      <c r="O21" s="10" t="inlineStr">
+        <is>
+          <t>atm</t>
+        </is>
+      </c>
+      <c r="P21" s="10" t="inlineStr">
+        <is>
+          <t>atm</t>
+        </is>
+      </c>
+      <c r="Q21" s="10" t="inlineStr">
+        <is>
+          <t>atm</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr"/>
@@ -25277,6 +25744,21 @@
           <t>0.975 / 1.0 / 1.0</t>
         </is>
       </c>
+      <c r="O22" s="10" t="inlineStr">
+        <is>
+          <t>0.975 / 1.0 / 1.0</t>
+        </is>
+      </c>
+      <c r="P22" s="10" t="inlineStr">
+        <is>
+          <t>0.975 / 1.0 / 1.0</t>
+        </is>
+      </c>
+      <c r="Q22" s="10" t="inlineStr">
+        <is>
+          <t>0.975 / 1.0 / 1.0</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr"/>
@@ -25345,6 +25827,21 @@
           <t>1,066 mm2</t>
         </is>
       </c>
+      <c r="O23" s="10" t="inlineStr">
+        <is>
+          <t>1,298 mm2</t>
+        </is>
+      </c>
+      <c r="P23" s="10" t="inlineStr">
+        <is>
+          <t>938 mm2</t>
+        </is>
+      </c>
+      <c r="Q23" s="10" t="inlineStr">
+        <is>
+          <t>10 mm2</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr"/>
@@ -25413,6 +25910,21 @@
           <t>K / 1,186 mm2 each</t>
         </is>
       </c>
+      <c r="O24" s="10" t="inlineStr">
+        <is>
+          <t>L / 1,841 mm2 each</t>
+        </is>
+      </c>
+      <c r="P24" s="10" t="inlineStr">
+        <is>
+          <t>K / 1,186 mm2 each</t>
+        </is>
+      </c>
+      <c r="Q24" s="10" t="inlineStr">
+        <is>
+          <t>D / 71 mm2 each</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr"/>
@@ -25481,6 +25993,21 @@
           <t>90 %</t>
         </is>
       </c>
+      <c r="O25" s="10" t="inlineStr">
+        <is>
+          <t>70 %</t>
+        </is>
+      </c>
+      <c r="P25" s="10" t="inlineStr">
+        <is>
+          <t>79 %</t>
+        </is>
+      </c>
+      <c r="Q25" s="10" t="inlineStr">
+        <is>
+          <t>14 %</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr"/>
@@ -25545,6 +26072,21 @@
         </is>
       </c>
       <c r="N26" s="10" t="inlineStr">
+        <is>
+          <t>&lt; 3 % of set (API 520-II)</t>
+        </is>
+      </c>
+      <c r="O26" s="10" t="inlineStr">
+        <is>
+          <t>&lt; 3 % of set (API 520-II)</t>
+        </is>
+      </c>
+      <c r="P26" s="10" t="inlineStr">
+        <is>
+          <t>&lt; 3 % of set (API 520-II)</t>
+        </is>
+      </c>
+      <c r="Q26" s="10" t="inlineStr">
         <is>
           <t>&lt; 3 % of set (API 520-II)</t>
         </is>
@@ -25569,6 +26111,9 @@
       <c r="L27" s="8" t="n"/>
       <c r="M27" s="8" t="n"/>
       <c r="N27" s="8" t="n"/>
+      <c r="O27" s="8" t="n"/>
+      <c r="P27" s="8" t="n"/>
+      <c r="Q27" s="8" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr"/>
@@ -25637,6 +26182,21 @@
           <t>A216 WCC</t>
         </is>
       </c>
+      <c r="O28" s="10" t="inlineStr">
+        <is>
+          <t>A216 WCC</t>
+        </is>
+      </c>
+      <c r="P28" s="10" t="inlineStr">
+        <is>
+          <t>A216 WCC</t>
+        </is>
+      </c>
+      <c r="Q28" s="10" t="inlineStr">
+        <is>
+          <t>A216 WCC</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr"/>
@@ -25705,6 +26265,21 @@
           <t>316 SS</t>
         </is>
       </c>
+      <c r="O29" s="10" t="inlineStr">
+        <is>
+          <t>316 SS</t>
+        </is>
+      </c>
+      <c r="P29" s="10" t="inlineStr">
+        <is>
+          <t>316 SS</t>
+        </is>
+      </c>
+      <c r="Q29" s="10" t="inlineStr">
+        <is>
+          <t>316 SS</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr"/>
@@ -25773,6 +26348,21 @@
           <t>CS, aluminised (W &lt; 230 C) / tungsten (&gt; 230 C)</t>
         </is>
       </c>
+      <c r="O30" s="10" t="inlineStr">
+        <is>
+          <t>CS, aluminised (W &lt; 230 C) / tungsten (&gt; 230 C)</t>
+        </is>
+      </c>
+      <c r="P30" s="10" t="inlineStr">
+        <is>
+          <t>CS, aluminised (W &lt; 230 C) / tungsten (&gt; 230 C)</t>
+        </is>
+      </c>
+      <c r="Q30" s="10" t="inlineStr">
+        <is>
+          <t>CS, aluminised (W &lt; 230 C) / tungsten (&gt; 230 C)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr"/>
@@ -25841,6 +26431,21 @@
           <t>Inconel 625</t>
         </is>
       </c>
+      <c r="O31" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P31" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q31" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr"/>
@@ -25909,6 +26514,21 @@
           <t>316 SS (Stellited seats)</t>
         </is>
       </c>
+      <c r="O32" s="10" t="inlineStr">
+        <is>
+          <t>316 SS (Stellited seats)</t>
+        </is>
+      </c>
+      <c r="P32" s="10" t="inlineStr">
+        <is>
+          <t>316 SS (Stellited seats)</t>
+        </is>
+      </c>
+      <c r="Q32" s="10" t="inlineStr">
+        <is>
+          <t>316 SS (Stellited seats)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="9" t="inlineStr"/>
@@ -25977,6 +26597,21 @@
           <t>No / Yes</t>
         </is>
       </c>
+      <c r="O33" s="10" t="inlineStr">
+        <is>
+          <t>No / Yes</t>
+        </is>
+      </c>
+      <c r="P33" s="10" t="inlineStr">
+        <is>
+          <t>No / Yes</t>
+        </is>
+      </c>
+      <c r="Q33" s="10" t="inlineStr">
+        <is>
+          <t>No / Yes</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="9" t="inlineStr"/>
@@ -26045,6 +26680,21 @@
           <t>MR0103 (sour)</t>
         </is>
       </c>
+      <c r="O34" s="10" t="inlineStr">
+        <is>
+          <t>MR0103 (sour)</t>
+        </is>
+      </c>
+      <c r="P34" s="10" t="inlineStr">
+        <is>
+          <t>MR0103 (sour)</t>
+        </is>
+      </c>
+      <c r="Q34" s="10" t="inlineStr">
+        <is>
+          <t>MR0103 (sour)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="9" t="inlineStr"/>
@@ -26109,6 +26759,21 @@
         </is>
       </c>
       <c r="N35" s="10" t="inlineStr">
+        <is>
+          <t>ASME VIII-1 UG-125..137, API 520/521/526/527</t>
+        </is>
+      </c>
+      <c r="O35" s="10" t="inlineStr">
+        <is>
+          <t>ASME VIII-1 UG-125..137, API 520/521/526/527</t>
+        </is>
+      </c>
+      <c r="P35" s="10" t="inlineStr">
+        <is>
+          <t>ASME VIII-1 UG-125..137, API 520/521/526/527</t>
+        </is>
+      </c>
+      <c r="Q35" s="10" t="inlineStr">
         <is>
           <t>ASME VIII-1 UG-125..137, API 520/521/526/527</t>
         </is>
